--- a/output/yearly_benthic_cover_iteration_3_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_3_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.48153822893086</v>
+        <v>45.29925954428013</v>
       </c>
       <c r="M2" t="n">
-        <v>98.83024617568387</v>
+        <v>100.4889510808033</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05279957898391</v>
+        <v>87.98350782601817</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92467420209306</v>
+        <v>45.89806427145406</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228799028263197</v>
+        <v>2.228641437372927</v>
       </c>
       <c r="E3" t="n">
-        <v>5.705510095874324</v>
+        <v>5.686502466860768</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429330094210657</v>
+        <v>0.7428804791243092</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97145338099513</v>
+        <v>33.96294558771216</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17491843336902</v>
+        <v>34.17250203971822</v>
       </c>
       <c r="I3" t="n">
-        <v>6.585854322179527</v>
+        <v>6.547032820702859</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643331308881661</v>
+        <v>4.643002994526933</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94720042101609</v>
+        <v>12.01649217398183</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89173423570083</v>
+        <v>48.85042924635236</v>
       </c>
       <c r="M3" t="n">
-        <v>106.76360885881</v>
+        <v>106.7649856917883</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.22655961797081</v>
+        <v>86.98179712101138</v>
       </c>
       <c r="C4" t="n">
-        <v>42.73715754273218</v>
+        <v>42.52856938004987</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189446576257481</v>
+        <v>2.17989076410173</v>
       </c>
       <c r="E4" t="n">
-        <v>6.521396049222306</v>
+        <v>6.473327703023467</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444944387541796</v>
+        <v>0.7444369520234805</v>
       </c>
       <c r="G4" t="n">
-        <v>33.37164156674564</v>
+        <v>33.22001923091528</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24674418269226</v>
+        <v>34.2440997930801</v>
       </c>
       <c r="I4" t="n">
-        <v>5.499746562085305</v>
+        <v>5.467291727720582</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653090242213623</v>
+        <v>4.652730950146753</v>
       </c>
       <c r="K4" t="n">
-        <v>12.77344038202921</v>
+        <v>13.01820287898862</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30646167740029</v>
+        <v>44.2713657181642</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81705960216168</v>
+        <v>99.81813797720268</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.16474360646249</v>
+        <v>85.65196305548427</v>
       </c>
       <c r="C5" t="n">
-        <v>42.52901630864981</v>
+        <v>42.0471866578314</v>
       </c>
       <c r="D5" t="n">
-        <v>2.137993619191154</v>
+        <v>2.114409607842419</v>
       </c>
       <c r="E5" t="n">
-        <v>7.133350788120485</v>
+        <v>7.039572000490443</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458167775045857</v>
+        <v>0.7457592553121452</v>
       </c>
       <c r="G5" t="n">
-        <v>32.58739331908953</v>
+        <v>32.22213194866276</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30757176521094</v>
+        <v>34.30492574435867</v>
       </c>
       <c r="I5" t="n">
-        <v>4.591262477942137</v>
+        <v>4.564169153116934</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661354859403661</v>
+        <v>4.660995345700907</v>
       </c>
       <c r="K5" t="n">
-        <v>13.83525639353753</v>
+        <v>14.34803694451572</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48295655997697</v>
+        <v>43.452907182994</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84722926216429</v>
+        <v>99.84813078534111</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.93176079154927</v>
+        <v>84.13834624699996</v>
       </c>
       <c r="C6" t="n">
-        <v>42.00924703315119</v>
+        <v>41.2421683862008</v>
       </c>
       <c r="D6" t="n">
-        <v>2.078137865531758</v>
+        <v>2.040134632208683</v>
       </c>
       <c r="E6" t="n">
-        <v>7.572278212638713</v>
+        <v>7.427154956412772</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469383937123191</v>
+        <v>0.7468846861576087</v>
       </c>
       <c r="G6" t="n">
-        <v>31.67506927405932</v>
+        <v>31.09023297484182</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35916611076667</v>
+        <v>34.35669556324999</v>
       </c>
       <c r="I6" t="n">
-        <v>3.831805974138485</v>
+        <v>3.809214145644034</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668364960701995</v>
+        <v>4.668029288485054</v>
       </c>
       <c r="K6" t="n">
-        <v>15.06823920845073</v>
+        <v>15.86165375300003</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79497868956638</v>
+        <v>42.76939538432369</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87246493116831</v>
+        <v>99.87321752352452</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.39596904228763</v>
+        <v>82.45952389187669</v>
       </c>
       <c r="C7" t="n">
-        <v>41.06882727086636</v>
+        <v>40.15464241472593</v>
       </c>
       <c r="D7" t="n">
-        <v>2.003464427899456</v>
+        <v>1.958198838213634</v>
       </c>
       <c r="E7" t="n">
-        <v>7.83305998540118</v>
+        <v>7.658603173521369</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747892936458092</v>
+        <v>0.747844314930855</v>
       </c>
       <c r="G7" t="n">
-        <v>30.53689343444529</v>
+        <v>29.84158845694211</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40307507707222</v>
+        <v>34.40083848681932</v>
       </c>
       <c r="I7" t="n">
-        <v>3.197252328148316</v>
+        <v>3.17842365313154</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674330852863076</v>
+        <v>4.674026968317844</v>
       </c>
       <c r="K7" t="n">
-        <v>16.60403095771237</v>
+        <v>17.54047610812333</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22070271658407</v>
+        <v>42.19906997310508</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8935609451628</v>
+        <v>99.89418849595432</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.17550019397598</v>
+        <v>87.33004384477448</v>
       </c>
       <c r="C8" t="n">
-        <v>43.38553330296976</v>
+        <v>42.42869892365326</v>
       </c>
       <c r="D8" t="n">
-        <v>2.007660195552338</v>
+        <v>1.962422346287825</v>
       </c>
       <c r="E8" t="n">
-        <v>9.669877475551791</v>
+        <v>9.473887134118439</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494592158224329</v>
+        <v>0.7494572903043006</v>
       </c>
       <c r="G8" t="n">
-        <v>31.04939683497587</v>
+        <v>30.3344437752481</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47512392783191</v>
+        <v>34.47503535399782</v>
       </c>
       <c r="I8" t="n">
-        <v>5.539862445351432</v>
+        <v>5.650689880416103</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684120098890206</v>
+        <v>4.68410806440188</v>
       </c>
       <c r="K8" t="n">
-        <v>11.82449980602403</v>
+        <v>12.66995615522553</v>
       </c>
       <c r="L8" t="n">
-        <v>44.60569073097166</v>
+        <v>44.71339397060559</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81572383996546</v>
+        <v>99.81204904948439</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.00504544468575</v>
+        <v>85.20682751170676</v>
       </c>
       <c r="C9" t="n">
-        <v>42.07536431224435</v>
+        <v>41.18181225183763</v>
       </c>
       <c r="D9" t="n">
-        <v>1.909090364287113</v>
+        <v>1.866109648794183</v>
       </c>
       <c r="E9" t="n">
-        <v>9.965921266390756</v>
+        <v>9.795189652664236</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508025940811401</v>
+        <v>0.7508404497212644</v>
       </c>
       <c r="G9" t="n">
-        <v>29.52496864055794</v>
+        <v>28.84567551265165</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53691932773244</v>
+        <v>34.53866068717816</v>
       </c>
       <c r="I9" t="n">
-        <v>4.624827038629237</v>
+        <v>4.717598749939376</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692516213007126</v>
+        <v>4.692752810757903</v>
       </c>
       <c r="K9" t="n">
-        <v>13.99495455531426</v>
+        <v>14.79317248829323</v>
       </c>
       <c r="L9" t="n">
-        <v>43.77579606451497</v>
+        <v>43.86805165207979</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84611493207358</v>
+        <v>99.84303639221065</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.67210204961866</v>
+        <v>83.03130539117609</v>
       </c>
       <c r="C10" t="n">
-        <v>40.4601765589484</v>
+        <v>39.73751519190336</v>
       </c>
       <c r="D10" t="n">
-        <v>1.80428084275666</v>
+        <v>1.768677272080474</v>
       </c>
       <c r="E10" t="n">
-        <v>10.06211461344811</v>
+        <v>9.940025935432516</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519571245360198</v>
+        <v>0.7520273391515646</v>
       </c>
       <c r="G10" t="n">
-        <v>27.90404073986423</v>
+        <v>27.33959963713911</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59002772865691</v>
+        <v>34.59325760097197</v>
       </c>
       <c r="I10" t="n">
-        <v>3.859948972006617</v>
+        <v>3.937546736703181</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699732028350124</v>
+        <v>4.700170869697279</v>
       </c>
       <c r="K10" t="n">
-        <v>16.32789795038132</v>
+        <v>16.9686946088239</v>
       </c>
       <c r="L10" t="n">
-        <v>43.0834580729306</v>
+        <v>43.1627457895522</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87153258226033</v>
+        <v>99.86895559027947</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.1787424408946</v>
+        <v>80.67632658863812</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56513773577072</v>
+        <v>37.99223287247445</v>
       </c>
       <c r="D11" t="n">
-        <v>1.693400269343938</v>
+        <v>1.664265763644765</v>
       </c>
       <c r="E11" t="n">
-        <v>9.980568803351026</v>
+        <v>9.900853663763327</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529516223130959</v>
+        <v>0.753048278460258</v>
       </c>
       <c r="G11" t="n">
-        <v>26.18922120376534</v>
+        <v>25.72564276484648</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63577462640241</v>
+        <v>34.64022080917186</v>
       </c>
       <c r="I11" t="n">
-        <v>3.220878276261936</v>
+        <v>3.285743568374817</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705947639456849</v>
+        <v>4.706551740376614</v>
       </c>
       <c r="K11" t="n">
-        <v>18.82125755910542</v>
+        <v>19.32367341136189</v>
       </c>
       <c r="L11" t="n">
-        <v>42.50638390034588</v>
+        <v>42.5747174179219</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89277919522202</v>
+        <v>99.89062370175823</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.5562621233165</v>
+        <v>78.29474632277832</v>
       </c>
       <c r="C12" t="n">
-        <v>36.44100578623167</v>
+        <v>36.11858347824044</v>
       </c>
       <c r="D12" t="n">
-        <v>1.57790908145898</v>
+        <v>1.559795477319075</v>
       </c>
       <c r="E12" t="n">
-        <v>9.747740683428926</v>
+        <v>9.736237233087472</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538101473803882</v>
+        <v>0.7539271551187611</v>
       </c>
       <c r="G12" t="n">
-        <v>24.40309637470965</v>
+        <v>24.11077732432327</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67526677949785</v>
+        <v>34.680649135463</v>
       </c>
       <c r="I12" t="n">
-        <v>2.687125635713272</v>
+        <v>2.74131527797449</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711313421127426</v>
+        <v>4.712044719492257</v>
       </c>
       <c r="K12" t="n">
-        <v>21.44373787668352</v>
+        <v>21.70525367722168</v>
       </c>
       <c r="L12" t="n">
-        <v>42.02578749607754</v>
+        <v>42.08489218986082</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91053115899274</v>
+        <v>99.90872934532294</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.87468937063565</v>
+        <v>75.86295728773952</v>
       </c>
       <c r="C13" t="n">
-        <v>34.17419542814621</v>
+        <v>34.10968638786176</v>
       </c>
       <c r="D13" t="n">
-        <v>1.46091843904665</v>
+        <v>1.454126134137002</v>
       </c>
       <c r="E13" t="n">
-        <v>9.39859502349791</v>
+        <v>9.457770392715146</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545524448429124</v>
+        <v>0.7546846718799208</v>
       </c>
       <c r="G13" t="n">
-        <v>22.59378178537506</v>
+        <v>22.47737727892149</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70941246277397</v>
+        <v>34.71549490647635</v>
       </c>
       <c r="I13" t="n">
-        <v>2.241476434830963</v>
+        <v>2.286724704360091</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715952780268203</v>
+        <v>4.716779199249506</v>
       </c>
       <c r="K13" t="n">
-        <v>24.12531062936432</v>
+        <v>24.13704271226051</v>
       </c>
       <c r="L13" t="n">
-        <v>41.62585156371968</v>
+        <v>41.67712325326733</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92535762123021</v>
+        <v>99.92385235338959</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.16939841476774</v>
+        <v>82.83217789583601</v>
       </c>
       <c r="C14" t="n">
-        <v>38.67928409443627</v>
+        <v>38.50789278352022</v>
       </c>
       <c r="D14" t="n">
-        <v>1.462664156227263</v>
+        <v>1.455797352902896</v>
       </c>
       <c r="E14" t="n">
-        <v>11.89667273019146</v>
+        <v>11.89111138766522</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554540935122903</v>
+        <v>0.7555520266137156</v>
       </c>
       <c r="G14" t="n">
-        <v>24.61071273154393</v>
+        <v>24.44968891506544</v>
       </c>
       <c r="H14" t="n">
-        <v>36.74082092121333</v>
+        <v>36.70187174051355</v>
       </c>
       <c r="I14" t="n">
-        <v>2.98148569762765</v>
+        <v>2.855956306739473</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721588084451814</v>
+        <v>4.722200166335723</v>
       </c>
       <c r="K14" t="n">
-        <v>16.83060158523224</v>
+        <v>17.16782210416397</v>
       </c>
       <c r="L14" t="n">
-        <v>44.39085007905245</v>
+        <v>44.22919585429279</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90073575872097</v>
+        <v>99.90491074197698</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.20434042149313</v>
+        <v>82.08423340735561</v>
       </c>
       <c r="C15" t="n">
-        <v>38.16588848421519</v>
+        <v>38.2008657919251</v>
       </c>
       <c r="D15" t="n">
-        <v>1.425925321261794</v>
+        <v>1.428369535292354</v>
       </c>
       <c r="E15" t="n">
-        <v>12.02102910356367</v>
+        <v>12.0641223155783</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756215964300215</v>
+        <v>0.756282952970824</v>
       </c>
       <c r="G15" t="n">
-        <v>24.00120815792857</v>
+        <v>23.98904677496282</v>
       </c>
       <c r="H15" t="n">
-        <v>36.78653500794484</v>
+        <v>36.73737738997966</v>
       </c>
       <c r="I15" t="n">
-        <v>2.487077089617703</v>
+        <v>2.382265982504003</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726349776876343</v>
+        <v>4.726768456067651</v>
       </c>
       <c r="K15" t="n">
-        <v>17.79565957850685</v>
+        <v>17.91576659264441</v>
       </c>
       <c r="L15" t="n">
-        <v>43.95563289012163</v>
+        <v>43.80403549579884</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91718095284367</v>
+        <v>99.92066788036833</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.53879722969265</v>
+        <v>79.61068079659759</v>
       </c>
       <c r="C16" t="n">
-        <v>35.88426272881175</v>
+        <v>36.09513924339406</v>
       </c>
       <c r="D16" t="n">
-        <v>1.325579971691178</v>
+        <v>1.335215729602623</v>
       </c>
       <c r="E16" t="n">
-        <v>11.52081178765161</v>
+        <v>11.60848341924088</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568733661923883</v>
+        <v>0.7569121140760739</v>
       </c>
       <c r="G16" t="n">
-        <v>22.3121929010894</v>
+        <v>22.42455597146821</v>
       </c>
       <c r="H16" t="n">
-        <v>36.81851467891503</v>
+        <v>36.76793966679929</v>
       </c>
       <c r="I16" t="n">
-        <v>2.074365985450611</v>
+        <v>1.986873182435048</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730458538702426</v>
+        <v>4.730700712975463</v>
       </c>
       <c r="K16" t="n">
-        <v>20.46120277030737</v>
+        <v>20.38931920340242</v>
       </c>
       <c r="L16" t="n">
-        <v>43.58544902616926</v>
+        <v>43.44936749813399</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93091452528837</v>
+        <v>99.93382594493045</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.28509077609868</v>
+        <v>81.3180578640073</v>
       </c>
       <c r="C17" t="n">
-        <v>37.1369474079206</v>
+        <v>37.35302768958938</v>
       </c>
       <c r="D17" t="n">
-        <v>1.326718732261475</v>
+        <v>1.336283838655001</v>
       </c>
       <c r="E17" t="n">
-        <v>12.31655141201383</v>
+        <v>12.39481743888092</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575235703026904</v>
+        <v>0.7575176077524701</v>
       </c>
       <c r="G17" t="n">
-        <v>22.76805677902016</v>
+        <v>22.89428944914693</v>
       </c>
       <c r="H17" t="n">
-        <v>37.2868404434263</v>
+        <v>37.24914716895739</v>
       </c>
       <c r="I17" t="n">
-        <v>2.094877524682411</v>
+        <v>1.951517312161654</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734522314391814</v>
+        <v>4.73448504845294</v>
       </c>
       <c r="K17" t="n">
-        <v>18.71490922390131</v>
+        <v>18.6819421359927</v>
       </c>
       <c r="L17" t="n">
-        <v>44.07837405379521</v>
+        <v>43.90003159311819</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93023068561712</v>
+        <v>99.93500141870027</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.7441313679671</v>
+        <v>78.91231456718162</v>
       </c>
       <c r="C18" t="n">
-        <v>34.91884629722801</v>
+        <v>35.2482091087432</v>
       </c>
       <c r="D18" t="n">
-        <v>1.235046534949648</v>
+        <v>1.249368123704699</v>
       </c>
       <c r="E18" t="n">
-        <v>11.75668584957652</v>
+        <v>11.85985352763623</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580837858377648</v>
+        <v>0.7580383421890893</v>
       </c>
       <c r="G18" t="n">
-        <v>21.19485385160279</v>
+        <v>21.40517951741668</v>
       </c>
       <c r="H18" t="n">
-        <v>37.31441538378347</v>
+        <v>37.27475306044698</v>
       </c>
       <c r="I18" t="n">
-        <v>1.747022300730875</v>
+        <v>1.627382357106123</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738023661486029</v>
+        <v>4.737739638681809</v>
       </c>
       <c r="K18" t="n">
-        <v>21.2558686320329</v>
+        <v>21.08768543281838</v>
       </c>
       <c r="L18" t="n">
-        <v>43.76709402838679</v>
+        <v>43.6098966442117</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94180895764771</v>
+        <v>99.94579118577329</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.74097174629064</v>
+        <v>77.9347981955401</v>
       </c>
       <c r="C19" t="n">
-        <v>34.17635785514658</v>
+        <v>34.52094846668104</v>
       </c>
       <c r="D19" t="n">
-        <v>1.199231216287923</v>
+        <v>1.214688101767253</v>
       </c>
       <c r="E19" t="n">
-        <v>11.659804076115</v>
+        <v>11.75680363556429</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585597564613529</v>
+        <v>0.7584782876492502</v>
       </c>
       <c r="G19" t="n">
-        <v>20.58022078053815</v>
+        <v>20.81101348968279</v>
       </c>
       <c r="H19" t="n">
-        <v>37.33784361940972</v>
+        <v>37.29638634398275</v>
       </c>
       <c r="I19" t="n">
-        <v>1.464313819595043</v>
+        <v>1.35693903908596</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740998477883455</v>
+        <v>4.740489297807815</v>
       </c>
       <c r="K19" t="n">
-        <v>22.25902825370934</v>
+        <v>22.06520180445989</v>
       </c>
       <c r="L19" t="n">
-        <v>43.5158340574062</v>
+        <v>43.3686446633839</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95122016626212</v>
+        <v>99.95479493452483</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.12600819621296</v>
+        <v>75.37840571349776</v>
       </c>
       <c r="C20" t="n">
-        <v>31.78622919871291</v>
+        <v>32.17305478804984</v>
       </c>
       <c r="D20" t="n">
-        <v>1.106049690096421</v>
+        <v>1.123331843776294</v>
       </c>
       <c r="E20" t="n">
-        <v>10.95731213524833</v>
+        <v>11.0611366794712</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589706850426423</v>
+        <v>0.7588577522464932</v>
       </c>
       <c r="G20" t="n">
-        <v>18.98111599103425</v>
+        <v>19.24582460321003</v>
       </c>
       <c r="H20" t="n">
-        <v>37.35807035431918</v>
+        <v>37.31504562329648</v>
       </c>
       <c r="I20" t="n">
-        <v>1.220922558955622</v>
+        <v>1.131348259956687</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743566781516514</v>
+        <v>4.742860951540584</v>
       </c>
       <c r="K20" t="n">
-        <v>24.87399180378706</v>
+        <v>24.62159428650224</v>
       </c>
       <c r="L20" t="n">
-        <v>43.29910361362238</v>
+        <v>43.1676581743622</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95932461612233</v>
+        <v>99.96230724891429</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.519797199753</v>
+        <v>81.23426569744983</v>
       </c>
       <c r="C21" t="n">
-        <v>35.77302010342033</v>
+        <v>35.8534148119417</v>
       </c>
       <c r="D21" t="n">
-        <v>1.10684069267886</v>
+        <v>1.124055657272533</v>
       </c>
       <c r="E21" t="n">
-        <v>13.09710286928747</v>
+        <v>13.03243363762397</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595134705768184</v>
+        <v>0.7593467186065629</v>
       </c>
       <c r="G21" t="n">
-        <v>20.8351465067181</v>
+        <v>20.96068077464532</v>
       </c>
       <c r="H21" t="n">
-        <v>39.22524333411553</v>
+        <v>39.04154461080017</v>
       </c>
       <c r="I21" t="n">
-        <v>1.748991135271091</v>
+        <v>1.570287307210245</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746959191105114</v>
+        <v>4.74591699129102</v>
       </c>
       <c r="K21" t="n">
-        <v>18.48020280024702</v>
+        <v>18.76573430255017</v>
       </c>
       <c r="L21" t="n">
-        <v>45.68851905564853</v>
+        <v>45.32854168045368</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94174195931589</v>
+        <v>99.94769079494554</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_3_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_3_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.29925954428013</v>
+        <v>45.45118304440633</v>
       </c>
       <c r="M2" t="n">
-        <v>100.4889510808033</v>
+        <v>99.91605076232742</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98350782601817</v>
+        <v>88.06504197285588</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89806427145406</v>
+        <v>45.93516874416683</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228641437372927</v>
+        <v>2.228822455527847</v>
       </c>
       <c r="E3" t="n">
-        <v>5.686502466860768</v>
+        <v>5.7121546886478</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428804791243092</v>
+        <v>0.7429408185092824</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96294558771216</v>
+        <v>33.97497186875671</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17250203971822</v>
+        <v>34.17527765142698</v>
       </c>
       <c r="I3" t="n">
-        <v>6.547032820702859</v>
+        <v>6.587494374304248</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643002994526933</v>
+        <v>4.643380115683015</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01649217398183</v>
+        <v>11.93495802714413</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85042924635236</v>
+        <v>48.89342570518294</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7649856917883</v>
+        <v>106.7635524764939</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.98179712101138</v>
+        <v>87.24925406858728</v>
       </c>
       <c r="C4" t="n">
-        <v>42.52856938004987</v>
+        <v>42.75803170138195</v>
       </c>
       <c r="D4" t="n">
-        <v>2.17989076410173</v>
+        <v>2.190037182281863</v>
       </c>
       <c r="E4" t="n">
-        <v>6.473327703023467</v>
+        <v>6.529606223548796</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444369520234805</v>
+        <v>0.7445022468099448</v>
       </c>
       <c r="G4" t="n">
-        <v>33.22001923091528</v>
+        <v>33.38375000441028</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2440997930801</v>
+        <v>34.24710335325745</v>
       </c>
       <c r="I4" t="n">
-        <v>5.467291727720582</v>
+        <v>5.501116015716788</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652730950146753</v>
+        <v>4.653139042562155</v>
       </c>
       <c r="K4" t="n">
-        <v>13.01820287898862</v>
+        <v>12.75074593141273</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2713657181642</v>
+        <v>44.30823641236353</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81813797720268</v>
+        <v>99.81701404515822</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.65196305548427</v>
+        <v>86.25357539762429</v>
       </c>
       <c r="C5" t="n">
-        <v>42.0471866578314</v>
+        <v>42.61626087715967</v>
       </c>
       <c r="D5" t="n">
-        <v>2.114409607842419</v>
+        <v>2.142041154679986</v>
       </c>
       <c r="E5" t="n">
-        <v>7.039572000490443</v>
+        <v>7.15190573087703</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457592553121452</v>
+        <v>0.7458235646469363</v>
       </c>
       <c r="G5" t="n">
-        <v>32.22213194866276</v>
+        <v>32.65212435000181</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30492574435867</v>
+        <v>34.30788397375906</v>
       </c>
       <c r="I5" t="n">
-        <v>4.564169153116934</v>
+        <v>4.592399344616101</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660995345700907</v>
+        <v>4.661397279043352</v>
       </c>
       <c r="K5" t="n">
-        <v>14.34803694451572</v>
+        <v>13.74642460237573</v>
       </c>
       <c r="L5" t="n">
-        <v>43.452907182994</v>
+        <v>43.48450574225026</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84813078534111</v>
+        <v>99.84719122178565</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.13834624699996</v>
+        <v>85.10200784294814</v>
       </c>
       <c r="C6" t="n">
-        <v>41.2421683862008</v>
+        <v>42.17816048783743</v>
       </c>
       <c r="D6" t="n">
-        <v>2.040134632208683</v>
+        <v>2.086361997992088</v>
       </c>
       <c r="E6" t="n">
-        <v>7.427154956412772</v>
+        <v>7.604793416314328</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468846861576087</v>
+        <v>0.7469432214654836</v>
       </c>
       <c r="G6" t="n">
-        <v>31.09023297484182</v>
+        <v>31.80338120428571</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35669556324999</v>
+        <v>34.35938818741224</v>
       </c>
       <c r="I6" t="n">
-        <v>3.809214145644034</v>
+        <v>3.832744681319022</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668029288485054</v>
+        <v>4.668395134159272</v>
       </c>
       <c r="K6" t="n">
-        <v>15.86165375300003</v>
+        <v>14.89799215705186</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76939538432369</v>
+        <v>42.79628070664916</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87321752352452</v>
+        <v>99.87243335153845</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.45952389187669</v>
+        <v>83.85351648427536</v>
       </c>
       <c r="C7" t="n">
-        <v>40.15464241472593</v>
+        <v>41.52531413156801</v>
       </c>
       <c r="D7" t="n">
-        <v>1.958198838213634</v>
+        <v>2.026159876381579</v>
       </c>
       <c r="E7" t="n">
-        <v>7.658603173521369</v>
+        <v>7.918358949453359</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747844314930855</v>
+        <v>0.7478927881178895</v>
       </c>
       <c r="G7" t="n">
-        <v>29.84158845694211</v>
+        <v>30.88569241167521</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40083848681932</v>
+        <v>34.40306825342291</v>
       </c>
       <c r="I7" t="n">
-        <v>3.17842365313154</v>
+        <v>3.198014279487591</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674026968317844</v>
+        <v>4.674329925736809</v>
       </c>
       <c r="K7" t="n">
-        <v>17.54047610812333</v>
+        <v>16.14648351572465</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19906997310508</v>
+        <v>42.2217372226707</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89418849595432</v>
+        <v>99.89353486996336</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.33004384477448</v>
+        <v>88.7249162864132</v>
       </c>
       <c r="C8" t="n">
-        <v>42.42869892365326</v>
+        <v>43.76957608900628</v>
       </c>
       <c r="D8" t="n">
-        <v>1.962422346287825</v>
+        <v>2.03049918786611</v>
       </c>
       <c r="E8" t="n">
-        <v>9.473887134118439</v>
+        <v>9.716122711999908</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494572903043006</v>
+        <v>0.7494945076082948</v>
       </c>
       <c r="G8" t="n">
-        <v>30.3344437752481</v>
+        <v>31.36719849573415</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47503535399782</v>
+        <v>34.47674734998155</v>
       </c>
       <c r="I8" t="n">
-        <v>5.650689880416103</v>
+        <v>5.700513360671351</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68410806440188</v>
+        <v>4.684340672551842</v>
       </c>
       <c r="K8" t="n">
-        <v>12.66995615522553</v>
+        <v>11.27508371358679</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71339397060559</v>
+        <v>44.76572916456025</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81204904948439</v>
+        <v>99.81038896715332</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.20682751170676</v>
+        <v>87.04132909333518</v>
       </c>
       <c r="C9" t="n">
-        <v>41.18181225183763</v>
+        <v>42.97146567689035</v>
       </c>
       <c r="D9" t="n">
-        <v>1.866109648794183</v>
+        <v>1.954764700516178</v>
       </c>
       <c r="E9" t="n">
-        <v>9.795189652664236</v>
+        <v>10.14690726327587</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508404497212644</v>
+        <v>0.7508604903296674</v>
       </c>
       <c r="G9" t="n">
-        <v>28.84567551265165</v>
+        <v>30.1972503805741</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53866068717816</v>
+        <v>34.53958255516469</v>
       </c>
       <c r="I9" t="n">
-        <v>4.717598749939376</v>
+        <v>4.759085638914271</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692752810757903</v>
+        <v>4.69287806456042</v>
       </c>
       <c r="K9" t="n">
-        <v>14.79317248829323</v>
+        <v>12.95867090666482</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86805165207979</v>
+        <v>43.91151582309285</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84303639221065</v>
+        <v>99.84165240664802</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.03130539117609</v>
+        <v>85.05180515490963</v>
       </c>
       <c r="C10" t="n">
-        <v>39.73751519190336</v>
+        <v>41.72124301278613</v>
       </c>
       <c r="D10" t="n">
-        <v>1.768677272080474</v>
+        <v>1.865722524409821</v>
       </c>
       <c r="E10" t="n">
-        <v>9.940025935432516</v>
+        <v>10.34671500252253</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520273391515646</v>
+        <v>0.7520293766860178</v>
       </c>
       <c r="G10" t="n">
-        <v>27.33959963713911</v>
+        <v>28.82172478119898</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59325760097197</v>
+        <v>34.5933513275568</v>
       </c>
       <c r="I10" t="n">
-        <v>3.937546736703181</v>
+        <v>3.972078538247853</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700170869697279</v>
+        <v>4.70018360428761</v>
       </c>
       <c r="K10" t="n">
-        <v>16.9686946088239</v>
+        <v>14.94819484509037</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1627457895522</v>
+        <v>43.19836531882033</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86895559027947</v>
+        <v>99.86780317669684</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.67632658863812</v>
+        <v>82.91346210760284</v>
       </c>
       <c r="C11" t="n">
-        <v>37.99223287247445</v>
+        <v>40.1995262122672</v>
       </c>
       <c r="D11" t="n">
-        <v>1.664265763644765</v>
+        <v>1.77085385085789</v>
       </c>
       <c r="E11" t="n">
-        <v>9.900853663763327</v>
+        <v>10.37301562611022</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753048278460258</v>
+        <v>0.7530314589979985</v>
       </c>
       <c r="G11" t="n">
-        <v>25.72564276484648</v>
+        <v>27.35619131429929</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64022080917186</v>
+        <v>34.63944711390791</v>
       </c>
       <c r="I11" t="n">
-        <v>3.285743568374817</v>
+        <v>3.314476124692047</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706551740376614</v>
+        <v>4.706446618737489</v>
       </c>
       <c r="K11" t="n">
-        <v>19.32367341136189</v>
+        <v>17.08653789239716</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5747174179219</v>
+        <v>42.60360038038429</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89062370175823</v>
+        <v>99.88966448504866</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.29474632277832</v>
+        <v>80.49196812995959</v>
       </c>
       <c r="C12" t="n">
-        <v>36.11858347824044</v>
+        <v>38.29194217882937</v>
       </c>
       <c r="D12" t="n">
-        <v>1.559795477319075</v>
+        <v>1.664197774279719</v>
       </c>
       <c r="E12" t="n">
-        <v>9.736237233087472</v>
+        <v>10.20913431355685</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539271551187611</v>
+        <v>0.7538937820758633</v>
       </c>
       <c r="G12" t="n">
-        <v>24.11077732432327</v>
+        <v>25.70856577236566</v>
       </c>
       <c r="H12" t="n">
-        <v>34.680649135463</v>
+        <v>34.6791139754897</v>
       </c>
       <c r="I12" t="n">
-        <v>2.74131527797449</v>
+        <v>2.765226374217654</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712044719492257</v>
+        <v>4.711836137974145</v>
       </c>
       <c r="K12" t="n">
-        <v>21.70525367722168</v>
+        <v>19.50803187004042</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08489218986082</v>
+        <v>42.10795716988877</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90872934532294</v>
+        <v>99.90793121875856</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.86295728773952</v>
+        <v>77.96487691639565</v>
       </c>
       <c r="C13" t="n">
-        <v>34.10968638786176</v>
+        <v>36.1927596473555</v>
       </c>
       <c r="D13" t="n">
-        <v>1.454126134137002</v>
+        <v>1.553824222985834</v>
       </c>
       <c r="E13" t="n">
-        <v>9.457770392715146</v>
+        <v>9.916478235363503</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546846718799208</v>
+        <v>0.7546372589015169</v>
       </c>
       <c r="G13" t="n">
-        <v>22.47737727892149</v>
+        <v>24.0035125948991</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71549490647635</v>
+        <v>34.71331390946976</v>
       </c>
       <c r="I13" t="n">
-        <v>2.286724704360091</v>
+        <v>2.306627826641459</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716779199249506</v>
+        <v>4.71648286813448</v>
       </c>
       <c r="K13" t="n">
-        <v>24.13704271226051</v>
+        <v>22.03512308360435</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67712325326733</v>
+        <v>41.69530542531189</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92385235338959</v>
+        <v>99.92318815627173</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.83217789583601</v>
+        <v>84.29169312035457</v>
       </c>
       <c r="C14" t="n">
-        <v>38.50789278352022</v>
+        <v>39.9433969605594</v>
       </c>
       <c r="D14" t="n">
-        <v>1.455797352902896</v>
+        <v>1.555806631478215</v>
       </c>
       <c r="E14" t="n">
-        <v>11.89111138766522</v>
+        <v>12.05782578415949</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555520266137156</v>
+        <v>0.7556000443238207</v>
       </c>
       <c r="G14" t="n">
-        <v>24.44968891506544</v>
+        <v>25.62512530309906</v>
       </c>
       <c r="H14" t="n">
-        <v>36.70187174051355</v>
+        <v>36.34859045477796</v>
       </c>
       <c r="I14" t="n">
-        <v>2.855956306739473</v>
+        <v>3.226244625492128</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722200166335723</v>
+        <v>4.722500277023878</v>
       </c>
       <c r="K14" t="n">
-        <v>17.16782210416397</v>
+        <v>15.70830687964545</v>
       </c>
       <c r="L14" t="n">
-        <v>44.22919585429279</v>
+        <v>44.24089170162019</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90491074197698</v>
+        <v>99.89259554182505</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.08423340735561</v>
+        <v>83.4356974795447</v>
       </c>
       <c r="C15" t="n">
-        <v>38.2008657919251</v>
+        <v>39.58645165356911</v>
       </c>
       <c r="D15" t="n">
-        <v>1.428369535292354</v>
+        <v>1.523503012628421</v>
       </c>
       <c r="E15" t="n">
-        <v>12.0641223155783</v>
+        <v>12.25603734244598</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756282952970824</v>
+        <v>0.7564125035815532</v>
       </c>
       <c r="G15" t="n">
-        <v>23.98904677496282</v>
+        <v>25.09306414329863</v>
       </c>
       <c r="H15" t="n">
-        <v>36.73737738997966</v>
+        <v>36.38767429158072</v>
       </c>
       <c r="I15" t="n">
-        <v>2.382265982504003</v>
+        <v>2.691428038624694</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726768456067651</v>
+        <v>4.727578147384706</v>
       </c>
       <c r="K15" t="n">
-        <v>17.91576659264441</v>
+        <v>16.56430252045529</v>
       </c>
       <c r="L15" t="n">
-        <v>43.80403549579884</v>
+        <v>43.75962791971195</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92066788036833</v>
+        <v>99.91038209373635</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.61068079659759</v>
+        <v>80.95963159466382</v>
       </c>
       <c r="C16" t="n">
-        <v>36.09513924339406</v>
+        <v>37.52676056688269</v>
       </c>
       <c r="D16" t="n">
-        <v>1.335215729602623</v>
+        <v>1.427779013004501</v>
       </c>
       <c r="E16" t="n">
-        <v>11.60848341924088</v>
+        <v>11.86012693248579</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569121140760739</v>
+        <v>0.7571116557043785</v>
       </c>
       <c r="G16" t="n">
-        <v>22.42455597146821</v>
+        <v>23.51642895275045</v>
       </c>
       <c r="H16" t="n">
-        <v>36.76793966679929</v>
+        <v>36.42130742112998</v>
       </c>
       <c r="I16" t="n">
-        <v>1.986873182435048</v>
+        <v>2.244929771436361</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730700712975463</v>
+        <v>4.731947848152365</v>
       </c>
       <c r="K16" t="n">
-        <v>20.38931920340242</v>
+        <v>19.04036840533617</v>
       </c>
       <c r="L16" t="n">
-        <v>43.44936749813399</v>
+        <v>43.35810913781934</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93382594493045</v>
+        <v>99.92523811003819</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.3180578640073</v>
+        <v>82.45537330946907</v>
       </c>
       <c r="C17" t="n">
-        <v>37.35302768958938</v>
+        <v>38.61012391092555</v>
       </c>
       <c r="D17" t="n">
-        <v>1.336283838655001</v>
+        <v>1.429097233951762</v>
       </c>
       <c r="E17" t="n">
-        <v>12.39481743888092</v>
+        <v>12.58622054653834</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575176077524701</v>
+        <v>0.7578106717529931</v>
       </c>
       <c r="G17" t="n">
-        <v>22.89428944914693</v>
+        <v>23.87264290387682</v>
       </c>
       <c r="H17" t="n">
-        <v>37.24914716895739</v>
+        <v>36.78943601798509</v>
       </c>
       <c r="I17" t="n">
-        <v>1.951517312161654</v>
+        <v>2.283849236907854</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73448504845294</v>
+        <v>4.736316698456206</v>
       </c>
       <c r="K17" t="n">
-        <v>18.6819421359927</v>
+        <v>17.54462669053094</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90003159311819</v>
+        <v>43.76919131255154</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93500141870027</v>
+        <v>99.92394191400803</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.91231456718162</v>
+        <v>80.08782981581561</v>
       </c>
       <c r="C18" t="n">
-        <v>35.2482091087432</v>
+        <v>36.59542914537035</v>
       </c>
       <c r="D18" t="n">
-        <v>1.249368123704699</v>
+        <v>1.340857921662888</v>
       </c>
       <c r="E18" t="n">
-        <v>11.85985352763623</v>
+        <v>12.12653971738428</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580383421890893</v>
+        <v>0.7584114348918367</v>
       </c>
       <c r="G18" t="n">
-        <v>21.40517951741668</v>
+        <v>22.39863151940929</v>
       </c>
       <c r="H18" t="n">
-        <v>37.27475306044698</v>
+        <v>36.81860126714597</v>
       </c>
       <c r="I18" t="n">
-        <v>1.627382357106123</v>
+        <v>1.904716487247365</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737739638681809</v>
+        <v>4.740071468073978</v>
       </c>
       <c r="K18" t="n">
-        <v>21.08768543281838</v>
+        <v>19.91217018418438</v>
       </c>
       <c r="L18" t="n">
-        <v>43.6098966442117</v>
+        <v>43.42896041386451</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94579118577329</v>
+        <v>99.93655974341924</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.9347981955401</v>
+        <v>79.15202790412755</v>
       </c>
       <c r="C19" t="n">
-        <v>34.52094846668104</v>
+        <v>35.95318263822237</v>
       </c>
       <c r="D19" t="n">
-        <v>1.214688101767253</v>
+        <v>1.306746287899198</v>
       </c>
       <c r="E19" t="n">
-        <v>11.75680363556429</v>
+        <v>12.08275957168655</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584782876492502</v>
+        <v>0.7589187304570431</v>
       </c>
       <c r="G19" t="n">
-        <v>20.81101348968279</v>
+        <v>21.82880685502547</v>
       </c>
       <c r="H19" t="n">
-        <v>37.29638634398275</v>
+        <v>36.84322894584465</v>
       </c>
       <c r="I19" t="n">
-        <v>1.35693903908596</v>
+        <v>1.588325447858135</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740489297807815</v>
+        <v>4.743242065356518</v>
       </c>
       <c r="K19" t="n">
-        <v>22.06520180445989</v>
+        <v>20.84797209587244</v>
       </c>
       <c r="L19" t="n">
-        <v>43.3686446633839</v>
+        <v>43.14593647459274</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95479493452483</v>
+        <v>99.94709120868755</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.37840571349776</v>
+        <v>76.64539039573643</v>
       </c>
       <c r="C20" t="n">
-        <v>32.17305478804984</v>
+        <v>33.69119469332409</v>
       </c>
       <c r="D20" t="n">
-        <v>1.123331843776294</v>
+        <v>1.21443866127353</v>
       </c>
       <c r="E20" t="n">
-        <v>11.0611366794712</v>
+        <v>11.44996986178913</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588577522464932</v>
+        <v>0.7593558460443909</v>
       </c>
       <c r="G20" t="n">
-        <v>19.24582460321003</v>
+        <v>20.28683549339498</v>
       </c>
       <c r="H20" t="n">
-        <v>37.31504562329648</v>
+        <v>36.86444959703448</v>
       </c>
       <c r="I20" t="n">
-        <v>1.131348259956687</v>
+        <v>1.324366898422486</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742860951540584</v>
+        <v>4.745974037777442</v>
       </c>
       <c r="K20" t="n">
-        <v>24.62159428650224</v>
+        <v>23.35460960426357</v>
       </c>
       <c r="L20" t="n">
-        <v>43.1676581743622</v>
+        <v>42.91007555108295</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96230724891429</v>
+        <v>99.95587984867061</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.23426569744983</v>
+        <v>82.42283819055034</v>
       </c>
       <c r="C21" t="n">
-        <v>35.8534148119417</v>
+        <v>37.13131007594471</v>
       </c>
       <c r="D21" t="n">
-        <v>1.124055657272533</v>
+        <v>1.215458376872717</v>
       </c>
       <c r="E21" t="n">
-        <v>13.03243363762397</v>
+        <v>13.34439307369318</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593467186065629</v>
+        <v>0.7599934467946287</v>
       </c>
       <c r="G21" t="n">
-        <v>20.96068077464532</v>
+        <v>21.84264285540733</v>
       </c>
       <c r="H21" t="n">
-        <v>39.04154461080017</v>
+        <v>38.43417651895368</v>
       </c>
       <c r="I21" t="n">
-        <v>1.570287307210245</v>
+        <v>2.07621487636238</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74591699129102</v>
+        <v>4.749959042466428</v>
       </c>
       <c r="K21" t="n">
-        <v>18.76573430255017</v>
+        <v>17.57716180944968</v>
       </c>
       <c r="L21" t="n">
-        <v>45.32854168045368</v>
+        <v>45.22237901379605</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94769079494554</v>
+        <v>99.93085089919043</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_3_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_3_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.45118304440633</v>
+        <v>44.12664262002261</v>
       </c>
       <c r="M2" t="n">
-        <v>99.91605076232742</v>
+        <v>94.12842911401475</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06504197285588</v>
+        <v>81.48941761200909</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93516874416683</v>
+        <v>43.24497316756463</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228822455527847</v>
+        <v>2.181133121144787</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7121546886478</v>
+        <v>4.147473126442756</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429408185092824</v>
+        <v>0.737641811330079</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97497186875671</v>
+        <v>32.80787736388618</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17527765142698</v>
+        <v>33.93152332118363</v>
       </c>
       <c r="I3" t="n">
-        <v>6.587494374304248</v>
+        <v>3.073507547208662</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643380115683015</v>
+        <v>4.610261320812993</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93495802714413</v>
+        <v>18.51058238799092</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89342570518294</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7635524764939</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.24925406858728</v>
+        <v>88.63348008655089</v>
       </c>
       <c r="C4" t="n">
-        <v>42.75803170138195</v>
+        <v>42.87426757542348</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190037182281863</v>
+        <v>2.186877557531248</v>
       </c>
       <c r="E4" t="n">
-        <v>6.529606223548796</v>
+        <v>6.552814423635337</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445022468099448</v>
+        <v>0.7395845338627393</v>
       </c>
       <c r="G4" t="n">
-        <v>33.38375000441028</v>
+        <v>33.50790874538803</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24710335325745</v>
+        <v>34.020888557686</v>
       </c>
       <c r="I4" t="n">
-        <v>5.501116015716788</v>
+        <v>7.003002931805408</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653139042562155</v>
+        <v>4.62240333664212</v>
       </c>
       <c r="K4" t="n">
-        <v>12.75074593141273</v>
+        <v>11.36651991344913</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30823641236353</v>
+        <v>45.52639225728446</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81701404515822</v>
+        <v>99.76717974615705</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.25357539762429</v>
+        <v>87.59632399732783</v>
       </c>
       <c r="C5" t="n">
-        <v>42.61626087715967</v>
+        <v>42.92266846727841</v>
       </c>
       <c r="D5" t="n">
-        <v>2.142041154679986</v>
+        <v>2.137938664968064</v>
       </c>
       <c r="E5" t="n">
-        <v>7.15190573087703</v>
+        <v>7.380976779669912</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458235646469363</v>
+        <v>0.7412306075413032</v>
       </c>
       <c r="G5" t="n">
-        <v>32.65212435000181</v>
+        <v>32.75805425972641</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30788397375906</v>
+        <v>34.09660794689994</v>
       </c>
       <c r="I5" t="n">
-        <v>4.592399344616101</v>
+        <v>5.84882444138904</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661397279043352</v>
+        <v>4.632691297133145</v>
       </c>
       <c r="K5" t="n">
-        <v>13.74642460237573</v>
+        <v>12.40367600267216</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48450574225026</v>
+        <v>44.47912767083263</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84719122178565</v>
+        <v>99.80547214078321</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.10200784294814</v>
+        <v>86.30461399794912</v>
       </c>
       <c r="C6" t="n">
-        <v>42.17816048783743</v>
+        <v>42.53882704049767</v>
       </c>
       <c r="D6" t="n">
-        <v>2.086361997992088</v>
+        <v>2.076526159610522</v>
       </c>
       <c r="E6" t="n">
-        <v>7.604793416314328</v>
+        <v>7.98282629754893</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469432214654836</v>
+        <v>0.7426285964928253</v>
       </c>
       <c r="G6" t="n">
-        <v>31.80338120428571</v>
+        <v>31.81707582302361</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35938818741224</v>
+        <v>34.16091543866996</v>
       </c>
       <c r="I6" t="n">
-        <v>3.832744681319022</v>
+        <v>4.883212954523113</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668395134159272</v>
+        <v>4.641428728080158</v>
       </c>
       <c r="K6" t="n">
-        <v>14.89799215705186</v>
+        <v>13.69538600205088</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79628070664916</v>
+        <v>43.60331961185729</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87243335153845</v>
+        <v>99.83753265440583</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.85351648427536</v>
+        <v>84.81011819839082</v>
       </c>
       <c r="C7" t="n">
-        <v>41.52531413156801</v>
+        <v>41.80278509857914</v>
       </c>
       <c r="D7" t="n">
-        <v>2.026159876381579</v>
+        <v>2.005626393789715</v>
       </c>
       <c r="E7" t="n">
-        <v>7.918358949453359</v>
+        <v>8.389575578625283</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478927881178895</v>
+        <v>0.7438182550356579</v>
       </c>
       <c r="G7" t="n">
-        <v>30.88569241167521</v>
+        <v>30.73073110518085</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40306825342291</v>
+        <v>34.21563973164026</v>
       </c>
       <c r="I7" t="n">
-        <v>3.198014279487591</v>
+        <v>4.075863040146198</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674329925736809</v>
+        <v>4.648864093972862</v>
       </c>
       <c r="K7" t="n">
-        <v>16.14648351572465</v>
+        <v>15.18988180160918</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2217372226707</v>
+        <v>42.87168829551938</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89353486996336</v>
+        <v>99.86435519570769</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.7249162864132</v>
+        <v>83.08765754558021</v>
       </c>
       <c r="C8" t="n">
-        <v>43.76957608900628</v>
+        <v>40.71338276873009</v>
       </c>
       <c r="D8" t="n">
-        <v>2.03049918786611</v>
+        <v>1.92424761629757</v>
       </c>
       <c r="E8" t="n">
-        <v>9.716122711999908</v>
+        <v>8.616031034384962</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494945076082948</v>
+        <v>0.7448331932122533</v>
       </c>
       <c r="G8" t="n">
-        <v>31.36719849573415</v>
+        <v>29.48382423532557</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47674734998155</v>
+        <v>34.26232688776365</v>
       </c>
       <c r="I8" t="n">
-        <v>5.700513360671351</v>
+        <v>3.401187121019637</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684340672551842</v>
+        <v>4.655207457576583</v>
       </c>
       <c r="K8" t="n">
-        <v>11.27508371358679</v>
+        <v>16.91234245441979</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76572916456025</v>
+        <v>42.26105635906828</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81038896715332</v>
+        <v>99.88678158221816</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87.04132909333518</v>
+        <v>81.14006463190907</v>
       </c>
       <c r="C9" t="n">
-        <v>42.97146567689035</v>
+        <v>39.29373026569081</v>
       </c>
       <c r="D9" t="n">
-        <v>1.954764700516178</v>
+        <v>1.832746766062135</v>
       </c>
       <c r="E9" t="n">
-        <v>10.14690726327587</v>
+        <v>8.679263657548672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508604903296674</v>
+        <v>0.7457014689675042</v>
       </c>
       <c r="G9" t="n">
-        <v>30.1972503805741</v>
+        <v>28.08182432487994</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53958255516469</v>
+        <v>34.30226757250519</v>
       </c>
       <c r="I9" t="n">
-        <v>4.759085638914271</v>
+        <v>2.837626660898719</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69287806456042</v>
+        <v>4.660634181046901</v>
       </c>
       <c r="K9" t="n">
-        <v>12.95867090666482</v>
+        <v>18.85993536809095</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91151582309285</v>
+        <v>41.75185694618992</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84165240664802</v>
+        <v>99.90552257997167</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85.05180515490963</v>
+        <v>85.92154157155987</v>
       </c>
       <c r="C10" t="n">
-        <v>41.72124301278613</v>
+        <v>42.54267808595922</v>
       </c>
       <c r="D10" t="n">
-        <v>1.865722524409821</v>
+        <v>1.834855585373542</v>
       </c>
       <c r="E10" t="n">
-        <v>10.34671500252253</v>
+        <v>10.53982451154382</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520293766860178</v>
+        <v>0.7465594978493024</v>
       </c>
       <c r="G10" t="n">
-        <v>28.82172478119898</v>
+        <v>29.47038950983188</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5933513275568</v>
+        <v>35.69799020609598</v>
       </c>
       <c r="I10" t="n">
-        <v>3.972078538247853</v>
+        <v>2.965925399307216</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70018360428761</v>
+        <v>4.66599686155814</v>
       </c>
       <c r="K10" t="n">
-        <v>14.94819484509037</v>
+        <v>14.07845842844011</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19836531882033</v>
+        <v>43.28011293129199</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86780317669684</v>
+        <v>99.90124944569132</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.91346210760284</v>
+        <v>85.63618678384351</v>
       </c>
       <c r="C11" t="n">
-        <v>40.1995262122672</v>
+        <v>42.64383310299941</v>
       </c>
       <c r="D11" t="n">
-        <v>1.77085385085789</v>
+        <v>1.817557200881746</v>
       </c>
       <c r="E11" t="n">
-        <v>10.37301562611022</v>
+        <v>10.89369460783563</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530314589979985</v>
+        <v>0.7472896814718303</v>
       </c>
       <c r="G11" t="n">
-        <v>27.35619131429929</v>
+        <v>29.22700004813695</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63944711390791</v>
+        <v>35.76735234464325</v>
       </c>
       <c r="I11" t="n">
-        <v>3.314476124692047</v>
+        <v>2.51273239167516</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706446618737489</v>
+        <v>4.670560509198939</v>
       </c>
       <c r="K11" t="n">
-        <v>17.08653789239716</v>
+        <v>14.36381321615649</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60360038038429</v>
+        <v>42.90867777491945</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88966448504866</v>
+        <v>99.91632409407535</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.49196812995959</v>
+        <v>83.77210314788191</v>
       </c>
       <c r="C12" t="n">
-        <v>38.29194217882937</v>
+        <v>41.17044851231945</v>
       </c>
       <c r="D12" t="n">
-        <v>1.664197774279719</v>
+        <v>1.738218155812329</v>
       </c>
       <c r="E12" t="n">
-        <v>10.20913431355685</v>
+        <v>10.76745044392614</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538937820758633</v>
+        <v>0.747912835354317</v>
       </c>
       <c r="G12" t="n">
-        <v>25.70856577236566</v>
+        <v>27.95119850916032</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6791139754897</v>
+        <v>35.79717821409181</v>
       </c>
       <c r="I12" t="n">
-        <v>2.765226374217654</v>
+        <v>2.095689768572525</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711836137974145</v>
+        <v>4.674455220964481</v>
       </c>
       <c r="K12" t="n">
-        <v>19.50803187004042</v>
+        <v>16.22789685211808</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10795716988877</v>
+        <v>42.53185651357148</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90793121875856</v>
+        <v>99.93020187800902</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.96487691639565</v>
+        <v>84.95432373333593</v>
       </c>
       <c r="C13" t="n">
-        <v>36.1927596473555</v>
+        <v>42.15457804247683</v>
       </c>
       <c r="D13" t="n">
-        <v>1.553824222985834</v>
+        <v>1.739549627274603</v>
       </c>
       <c r="E13" t="n">
-        <v>9.916478235363503</v>
+        <v>11.41364819374625</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546372589015169</v>
+        <v>0.7484857350178101</v>
       </c>
       <c r="G13" t="n">
-        <v>24.0035125948991</v>
+        <v>28.2851848048197</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71331390946976</v>
+        <v>36.13717451375199</v>
       </c>
       <c r="I13" t="n">
-        <v>2.306627826641459</v>
+        <v>1.952245014864261</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71648286813448</v>
+        <v>4.678035843861314</v>
       </c>
       <c r="K13" t="n">
-        <v>22.03512308360435</v>
+        <v>15.04567626666407</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69530542531189</v>
+        <v>42.73472066606293</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92318815627173</v>
+        <v>99.93497497520383</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.29169312035457</v>
+        <v>83.11497032204431</v>
       </c>
       <c r="C14" t="n">
-        <v>39.9433969605594</v>
+        <v>40.61866009052012</v>
       </c>
       <c r="D14" t="n">
-        <v>1.555806631478215</v>
+        <v>1.663420377789945</v>
       </c>
       <c r="E14" t="n">
-        <v>12.05782578415949</v>
+        <v>11.18546608862323</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556000443238207</v>
+        <v>0.748974409370968</v>
       </c>
       <c r="G14" t="n">
-        <v>25.62512530309906</v>
+        <v>27.04731848760549</v>
       </c>
       <c r="H14" t="n">
-        <v>36.34859045477796</v>
+        <v>36.16076789643689</v>
       </c>
       <c r="I14" t="n">
-        <v>3.226244625492128</v>
+        <v>1.627933003649233</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722500277023878</v>
+        <v>4.681090058568551</v>
       </c>
       <c r="K14" t="n">
-        <v>15.70830687964545</v>
+        <v>16.88502967795568</v>
       </c>
       <c r="L14" t="n">
-        <v>44.24089170162019</v>
+        <v>42.44208120333352</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89259554182505</v>
+        <v>99.94577097180934</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.4356974795447</v>
+        <v>82.31095822217435</v>
       </c>
       <c r="C15" t="n">
-        <v>39.58645165356911</v>
+        <v>40.04798563571678</v>
       </c>
       <c r="D15" t="n">
-        <v>1.523503012628421</v>
+        <v>1.629872208062998</v>
       </c>
       <c r="E15" t="n">
-        <v>12.25603734244598</v>
+        <v>11.1892153066984</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564125035815532</v>
+        <v>0.7493917769236191</v>
       </c>
       <c r="G15" t="n">
-        <v>25.09306414329863</v>
+        <v>26.50182316760312</v>
       </c>
       <c r="H15" t="n">
-        <v>36.38767429158072</v>
+        <v>36.18091855981081</v>
       </c>
       <c r="I15" t="n">
-        <v>2.691428038624694</v>
+        <v>1.37603859730278</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727578147384706</v>
+        <v>4.683698605772621</v>
       </c>
       <c r="K15" t="n">
-        <v>16.56430252045529</v>
+        <v>17.68904177782565</v>
       </c>
       <c r="L15" t="n">
-        <v>43.75962791971195</v>
+        <v>42.21713017899135</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91038209373635</v>
+        <v>99.95415759253379</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.95963159466382</v>
+        <v>80.04913913879125</v>
       </c>
       <c r="C16" t="n">
-        <v>37.52676056688269</v>
+        <v>37.99959984775265</v>
       </c>
       <c r="D16" t="n">
-        <v>1.427779013004501</v>
+        <v>1.536852473940507</v>
       </c>
       <c r="E16" t="n">
-        <v>11.86012693248579</v>
+        <v>10.74183446675805</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571116557043785</v>
+        <v>0.7497497808557719</v>
       </c>
       <c r="G16" t="n">
-        <v>23.51642895275045</v>
+        <v>24.98931652283896</v>
       </c>
       <c r="H16" t="n">
-        <v>36.42130742112998</v>
+        <v>36.19820312512388</v>
       </c>
       <c r="I16" t="n">
-        <v>2.244929771436361</v>
+        <v>1.147246638925508</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731947848152365</v>
+        <v>4.685936130348576</v>
       </c>
       <c r="K16" t="n">
-        <v>19.04036840533617</v>
+        <v>19.95086086120875</v>
       </c>
       <c r="L16" t="n">
-        <v>43.35810913781934</v>
+        <v>42.01131599666908</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92523811003819</v>
+        <v>99.96177670563048</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.45537330946907</v>
+        <v>84.67067718662494</v>
       </c>
       <c r="C17" t="n">
-        <v>38.61012391092555</v>
+        <v>41.01612933791169</v>
       </c>
       <c r="D17" t="n">
-        <v>1.429097233951762</v>
+        <v>1.537662509410299</v>
       </c>
       <c r="E17" t="n">
-        <v>12.58622054653834</v>
+        <v>12.35904379072463</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578106717529931</v>
+        <v>0.7501449547102963</v>
       </c>
       <c r="G17" t="n">
-        <v>23.87264290387682</v>
+        <v>26.39089663147022</v>
       </c>
       <c r="H17" t="n">
-        <v>36.78943601798509</v>
+        <v>37.60569115001821</v>
       </c>
       <c r="I17" t="n">
-        <v>2.283849236907854</v>
+        <v>1.33883218335193</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736316698456206</v>
+        <v>4.688405966939354</v>
       </c>
       <c r="K17" t="n">
-        <v>17.54462669053094</v>
+        <v>15.32932281337506</v>
       </c>
       <c r="L17" t="n">
-        <v>43.76919131255154</v>
+        <v>43.60994361901214</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92394191400803</v>
+        <v>99.95539577029889</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.08782981581561</v>
+        <v>86.3042955490146</v>
       </c>
       <c r="C18" t="n">
-        <v>36.59542914537035</v>
+        <v>41.75741548614509</v>
       </c>
       <c r="D18" t="n">
-        <v>1.340857921662888</v>
+        <v>1.538958351585742</v>
       </c>
       <c r="E18" t="n">
-        <v>12.12653971738428</v>
+        <v>12.97086134930732</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584114348918367</v>
+        <v>0.7507771281970399</v>
       </c>
       <c r="G18" t="n">
-        <v>22.39863151940929</v>
+        <v>26.53200909695533</v>
       </c>
       <c r="H18" t="n">
-        <v>36.81860126714597</v>
+        <v>37.63738278607659</v>
       </c>
       <c r="I18" t="n">
-        <v>1.904716487247365</v>
+        <v>2.181949785661074</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740071468073978</v>
+        <v>4.692357051231501</v>
       </c>
       <c r="K18" t="n">
-        <v>19.91217018418438</v>
+        <v>13.6957044509854</v>
       </c>
       <c r="L18" t="n">
-        <v>43.42896041386451</v>
+        <v>44.47420964525944</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93655974341924</v>
+        <v>99.92732958238993</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.15202790412755</v>
+        <v>83.78198934726369</v>
       </c>
       <c r="C19" t="n">
-        <v>35.95318263822237</v>
+        <v>39.57334830563634</v>
       </c>
       <c r="D19" t="n">
-        <v>1.306746287899198</v>
+        <v>1.445424294741936</v>
       </c>
       <c r="E19" t="n">
-        <v>12.08275957168655</v>
+        <v>12.48579266391171</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589187304570431</v>
+        <v>0.75132064992257</v>
       </c>
       <c r="G19" t="n">
-        <v>21.82880685502547</v>
+        <v>24.91945964459498</v>
       </c>
       <c r="H19" t="n">
-        <v>36.84322894584465</v>
+        <v>37.66463020008007</v>
       </c>
       <c r="I19" t="n">
-        <v>1.588325447858135</v>
+        <v>1.819607831996369</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743242065356518</v>
+        <v>4.695754062016064</v>
       </c>
       <c r="K19" t="n">
-        <v>20.84797209587244</v>
+        <v>16.21801065273631</v>
       </c>
       <c r="L19" t="n">
-        <v>43.14593647459274</v>
+        <v>44.14803132535899</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94709120868755</v>
+        <v>99.93939028373164</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.64539039573643</v>
+        <v>81.19505469414223</v>
       </c>
       <c r="C20" t="n">
-        <v>33.69119469332409</v>
+        <v>37.26778591004921</v>
       </c>
       <c r="D20" t="n">
-        <v>1.21443866127353</v>
+        <v>1.350018797326224</v>
       </c>
       <c r="E20" t="n">
-        <v>11.44996986178913</v>
+        <v>11.91454634467554</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593558460443909</v>
+        <v>0.7517886452100988</v>
       </c>
       <c r="G20" t="n">
-        <v>20.28683549339498</v>
+        <v>23.27464611034632</v>
       </c>
       <c r="H20" t="n">
-        <v>36.86444959703448</v>
+        <v>37.68809138065852</v>
       </c>
       <c r="I20" t="n">
-        <v>1.324366898422486</v>
+        <v>1.517284383362389</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745974037777442</v>
+        <v>4.69867903256312</v>
       </c>
       <c r="K20" t="n">
-        <v>23.35460960426357</v>
+        <v>18.80494530585779</v>
       </c>
       <c r="L20" t="n">
-        <v>42.91007555108295</v>
+        <v>43.87672412209311</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95587984867061</v>
+        <v>99.94945533800011</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.42283819055034</v>
+        <v>78.63602131077545</v>
       </c>
       <c r="C21" t="n">
-        <v>37.13131007594471</v>
+        <v>34.94270045632508</v>
       </c>
       <c r="D21" t="n">
-        <v>1.215458376872717</v>
+        <v>1.256143130475977</v>
       </c>
       <c r="E21" t="n">
-        <v>13.34439307369318</v>
+        <v>11.29689669523835</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7599934467946287</v>
+        <v>0.7521917997455363</v>
       </c>
       <c r="G21" t="n">
-        <v>21.84264285540733</v>
+        <v>21.65620721998449</v>
       </c>
       <c r="H21" t="n">
-        <v>38.43417651895368</v>
+        <v>37.70830201441697</v>
       </c>
       <c r="I21" t="n">
-        <v>2.07621487636238</v>
+        <v>1.265081702504522</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749959042466428</v>
+        <v>4.701198748409604</v>
       </c>
       <c r="K21" t="n">
-        <v>17.57716180944968</v>
+        <v>21.36397868922456</v>
       </c>
       <c r="L21" t="n">
-        <v>45.22237901379605</v>
+        <v>43.65117406602363</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93085089919043</v>
+        <v>99.95785321157327</v>
       </c>
     </row>
   </sheetData>
